--- a/FastAPI_AI_Service/app/data/NenThom_data/Policies/Tests/Results/Result_Test_Policies.xlsx
+++ b/FastAPI_AI_Service/app/data/NenThom_data/Policies/Tests/Results/Result_Test_Policies.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.88</v>
+        <v>7.26</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,27 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.49</v>
+        <v>11.49</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Avg_Judge_Latency</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>P95_Judge_Latency</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>11.46</v>
       </c>
     </row>
   </sheetData>
@@ -491,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -530,6 +550,11 @@
           <t>Response Time</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Judge Time</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -544,21 +569,26 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Deliveries within Hanoi or Ho Chi Minh City are usually completed within **2–4 hours** and at most **within 24 hours** of ordering.
-Note: For pre-orders or if inventory is insufficient, customer service will call to notify you, which may delay delivery.</t>
+          <t>Delivery within Hanoi or Ho Chi Minh City:
+- Usually: 2–4 hours from the time of order.  
+- Maximum: within 24 hours.  
+- Exception: for pre-orders or if inventory is insufficient, customer service will call to notify you.</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>7.15</v>
+        <v>6.12</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.89</v>
       </c>
     </row>
     <row r="3">
@@ -574,24 +604,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>### Payment methods supported
-- Cash on Delivery (COD) — delivery and collection at home (nationwide).  
+          <t>nenthom.com.vn supports the following payment methods:
+- Cash on delivery (COD) — delivery and collection at home, available nationwide.  
 - MoMo e-wallet.  
 - Zalo Pay e-wallet.  
-- Bank transfer via Internet banking — **admin will contact you** with details.</t>
+- Bank transfer via Internet banking — admin will contact you with payment details.</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>4.46</v>
+        <v>6.05</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.24</v>
       </c>
     </row>
     <row r="4">
@@ -607,20 +640,23 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Customers have **7 days** from the purchase date to return or exchange a product.</t>
+          <t>Customers have **7 days** to return a product.</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>3.22</v>
+        <v>4.69</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5.62</v>
       </c>
     </row>
     <row r="5">
@@ -636,22 +672,23 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No. Nenthom.com.vn does not sell customer information to third parties.
-- The site pledges not to sell, trade, exchange, lease, or otherwise commercially use customers’ confidential/personal data.  
-- If data were ever to be shared with an external party for a third‑party‑sponsored promotional or marketing campaign, customers would be notified in advance and given a clear opt‑in or opt‑out choice.</t>
+          <t>I don't know based on the provided documents, you should contact admin for detail information.</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>7.53</v>
+        <v>6.19</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.86</v>
       </c>
     </row>
     <row r="6">
@@ -667,8 +704,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>### Customer information collected
-The website may collect the following customer information:
+          <t>Nenthom collects the following customer information:
 - First name  
 - Last name  
 - Email address  
@@ -682,13 +718,16 @@
         <v>1</v>
       </c>
       <c r="E6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>5.83</v>
+        <v>5.65</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.54</v>
       </c>
     </row>
     <row r="7">
@@ -704,7 +743,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>If after 3 days in Da Nang you haven't received a delivery call from the postman, please contact **nenthom.com.vn** for support.</t>
+          <t>They should contact nenthom.com.vn for support.</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -717,7 +756,10 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>5.85</v>
+        <v>6.43</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4.35</v>
       </c>
     </row>
     <row r="8">
@@ -734,20 +776,18 @@
       <c r="C8" t="inlineStr">
         <is>
           <t>Exchange workflow
-1. Notify the store
-- Contact nenthom.com.vn via their Fanpage or hotline to start the exchange.
-2. Prepare the product for return
-- Ensure the product is intact, unused, undamaged, with all parts.
-- Include original packaging, purchase invoice/catalog, accessories, and any promotional gifts.
-- Note: the customer pays the cost of returning the product.
-3. Send the package
-- Ship the item to: **303B Vu Huu, Thanh Xuan Bac Ward, Thanh Xuan District, Hanoi**.
-4. Store receives and verifies
-- The store receives the returned item and checks that it meets the required conditions (intact, complete documents/gifts, no heavy use or damage).
-5. Replacement dispatched
-- Immediately after the store successfully receives and verifies the valid returned item, they will process and dispatch a replacement (a new order).
-6. Receive replacement
-- Wait to receive the replacement order sent by the store.</t>
+1. Notify the seller  
+   - Contact nenthom.com.vn via their Fanpage or hotline to start the exchange process.
+2. Prepare the item for return (mandatory for a full exchange within the 7-day window)  
+   - Ensure the product is fully intact, unused, and undamaged.  
+   - Keep the original packaging.  
+   - Include all accompanying documents (purchase invoice, catalog) and any promotional gifts or accessories.
+3. Ship the item back (customer pays return shipping)  
+   - Send the package to:  
+     303B Vu Huu, Thanh Xuan Bac Ward, Thanh Xuan District, Hanoi.
+4. Replacement sent  
+   - Immediately after the returned goods are received, a new order (replacement) will be sent to the customer.
+If you need help with the Fanpage or hotline contact details, you should contact admin for detail information.</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -760,7 +800,10 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>11.35</v>
+        <v>12.55</v>
+      </c>
+      <c r="H8" t="n">
+        <v>15.56</v>
       </c>
     </row>
     <row r="9">
@@ -776,22 +819,23 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>They may share customer information in these two cases:
-- To comply with Vietnamese law.  
-- To protect the legitimate interests and assets of the company and its partners, provided such disclosure is necessary and is in accordance with Vietnamese law.</t>
+          <t>I don't know based on the provided documents, you should contact admin for detail information.</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>9.449999999999999</v>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.16</v>
       </c>
     </row>
     <row r="10">
@@ -807,22 +851,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>### Geographical scopes collected below the country level
-- **State / Province (Province)**  
-- **Detailed street address**</t>
+          <t>They collect the following geographical details below the country level:
+- State/Province  
+- Detailed Street Address</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>5.92</v>
+        <v>5.42</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.38</v>
       </c>
     </row>
     <row r="11">
@@ -838,17 +885,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Inside Hanoi (or Ho Chi Minh)
-- Expected delivery time: usually within **2–4 hours**, and no later than **24 hours** from the time of order.
-- Handling when inventory is short: customer service will call you immediately to explain and arrange an alternative solution or switch the order to pre-order status.
-Outside areas — ordering as a holiday gift
-- Expected delivery time: typically **1–2 days**, can take up to **3 days**.
-- Holiday recommendation: place your gift order **1–3 days earlier** than the event to avoid delays from holiday overload.
-- If you don’t receive a delivery call within 3 days, contact nenthom.com.vn for support.</t>
+          <t>Inside Hanoi
+- Delivery time expectation: typically very fast — usually within **2–4 hours**, and at most **24 hours** from the time of order.  
+- If there is an inventory shortage for a Hanoi order, customer service will **call you immediately** to explain and arrange an alternative solution or switch the order to pre-order status.
+Holiday gift for an outside area
+- Delivery time expectation: generally **1–2 days**, and may take up to **3 days** for other areas.  
+- For holiday gifts: you should **order 1–3 days earlier** than needed to avoid delays from holiday overload.  
+- If you haven’t received a delivery call within **3 days** of ordering, contact nenthom.com.vn for support.</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
@@ -857,7 +904,10 @@
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>8</v>
+        <v>10.19</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6.44</v>
       </c>
     </row>
   </sheetData>
@@ -871,7 +921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -916,14 +966,14 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>144</v>
+        <v>302</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
           <t xml:space="preserve">Question:
-                    How long does delivery take within Hanoi or Ho Chi Minh City?
-                    Answer:
-                    Orders are usually delivered within 2–4 hours and no later </t>
+                    Under what circumstances will nenthom.com.vn's customer service call a customer regarding a delivery delay within Hanoi or Ho Chi Minh City?
+                    Answer:
+</t>
         </is>
       </c>
     </row>
@@ -938,29 +988,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FAQ_Policies.json</t>
+          <t>Chinh_sach_mua_hang.docx</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>177</v>
+        <v>4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Question:
-                    What is the expected delivery timeframe if a customer is located outside Hanoi and Ho Chi Minh City?
-                    Answer:
-                    The average delivery</t>
+          <t>## Average delivery time:
+Orders within Hanoi or Ho Chi Minh: Customers will receive within a maximum of 24 hours (Usually 2-4 hours) from the time of order. Except for pre-orders or insufficient inv</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>How long does delivery take within Hanoi or Ho Chi Minh City?</t>
+          <t>What payment methods are supported by nenthom.com.vn?</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -968,189 +1016,61 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>145</v>
+        <v>290</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>Question:
-                    How long does delivery take to other areas in Vietnam?
-                    Answer:
-                    Delivery usually takes 1–2 days and may take up to 3 days.</t>
+                    Does nenthom.com.vn accept Zalo Pay payments?
+                    Answer:
+                    Yes. Customers can pay using the Zalo Pay e-wallet.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>How long does delivery take within Hanoi or Ho Chi Minh City?</t>
+          <t>What payment methods are supported by nenthom.com.vn?</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chinh_sach_mua_hang.docx</t>
+          <t>FAQ_Candle_product.json</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>650</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>## Average delivery time:
-Orders within Hanoi or Ho Chi Minh: Customers will receive within a maximum of 24 hours (Usually 2-4 hours) from the time of order. Except for pre-orders or insufficient inv</t>
+          <t xml:space="preserve">Question:
+                    Which specific third-party digital mobile wallets are integrated as formal checkout gateways on nenthom.com.vn?
+                    Answer:
+                    MoMo and </t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>How long does delivery take within Hanoi or Ho Chi Minh City?</t>
+          <t>What payment methods are supported by nenthom.com.vn?</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Chinh_sach_mua_hang.docx</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>5</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>FAQ_Policies.json</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>162</v>
-      </c>
       <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question:
-                    Under what circumstances will nenthom.com.vn's customer service call a customer regarding a delivery delay within Hanoi or Ho Chi Minh City?
-                    Answer:
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>What payment methods are supported by nenthom.com.vn?</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>FAQ_Policies.json</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>147</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Question:
-                    What payment methods are supported by nenthom.com.vn?
-                    Answer:
-                    Supported payment methods include COD, MoMo, Zalo Pay, and bank tra</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>What payment methods are supported by nenthom.com.vn?</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>FAQ_Policies.json</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>149</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Question:
-                    Does nenthom.com.vn accept MoMo payments?
-                    Answer:
-                    Yes. Customers can pay using the MoMo e-wallet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>What payment methods are supported by nenthom.com.vn?</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>FAQ_Policies.json</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>150</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Question:
-                    Does nenthom.com.vn accept Zalo Pay payments?
-                    Answer:
-                    Yes. Customers can pay using the Zalo Pay e-wallet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>What payment methods are supported by nenthom.com.vn?</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>4</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>FAQ_Candle_product.json</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>510</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question:
-                    Which specific third-party digital mobile wallets are integrated as formal checkout gateways on nenthom.com.vn?
-                    Answer:
-                    MoMo and </t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>What payment methods are supported by nenthom.com.vn?</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Chinh_sach_mua_hang.docx</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>9</v>
-      </c>
-      <c r="E11" t="inlineStr">
         <is>
           <t># Payment policy
 Nenthom.com.vn is responsible for and protects your rights when making payment transactions.
@@ -1159,50 +1079,50 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>How many days do customers have to return a product?</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>FAQ_Policies.json</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>151</v>
-      </c>
-      <c r="E12" t="inlineStr">
+      <c r="D7" t="n">
+        <v>293</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>Question:
-                    How many days do I have to return a product?
-                    Answer:
-                    Customers can exchange or return products within 7 days from the purchase da</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+                    Do I need to provide invoices and accessories when returning a product?
+                    Answer:
+                    Yes. Customers must provide accompanying document</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>How many days do customers have to return a product?</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B8" t="n">
         <v>2</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>FAQ_Candle_product.json</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>455</v>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="D8" t="n">
+        <v>595</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t xml:space="preserve">Question:
                     What are the mandatory product condition parameters for a customer to claim a full return or exchange within the 7-day window?
@@ -1211,154 +1131,24 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>How many days do customers have to return a product?</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>3</v>
-      </c>
-      <c r="C14" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Does nenthom.com.vn sell customer information to third parties?</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>FAQ_Policies.json</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>152</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question:
-                    What condition must a product meet to be eligible for return?
-                    Answer:
-                    The product must remain intact, show no signs of heavy use </t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>How many days do customers have to return a product?</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>4</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>FAQ_Policies.json</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>154</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Question:
-                    Who pays for return shipping costs?
-                    Answer:
-                    The customer is responsible for the cost of returning the product.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>How many days do customers have to return a product?</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>5</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>FAQ_Policies.json</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>153</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Question:
-                    Do I need to provide invoices and accessories when returning a product?
-                    Answer:
-                    Yes. Customers must provide accompanying document</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Does nenthom.com.vn sell customer information to third parties?</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>FAQ_Policies.json</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>157</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Question:
-                    Does nenthom.com.vn sell customer information to third parties?
-                    Answer:
-                    No. Nenthom.com.vn commits not to trade or exchange custo</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Does nenthom.com.vn sell customer information to third parties?</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>FAQ_Policies.json</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>174</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Question:
-                    What absolute commitment does nenthom.com.vn make regarding the commercial use of customer information?
-                    Answer:
-                    The website commi</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Does nenthom.com.vn sell customer information to third parties?</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>3</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>FAQ_Policies.json</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>156</v>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="D9" t="n">
+        <v>296</v>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>Question:
                     What customer information does nenthom.com.vn collect?
@@ -1367,50 +1157,24 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Does nenthom.com.vn sell customer information to third parties?</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>4</v>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>FAQ_Candle_product.json</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>478</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Question:
-                    What is the definitive commercial pledge made by nenthom.com.vn regarding customer databases?
-                    Answer:
-                    The platform strictly pledg</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Does nenthom.com.vn sell customer information to third parties?</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>5</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>FAQ_Candle_product.json</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>464</v>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="D10" t="n">
+        <v>604</v>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>Question:
                     In what specific context does nenthom.com.vn explicitly state it will notify customers prior to sharing their personal data with external entities?
@@ -1418,76 +1182,24 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>What customer information does nenthom.com.vn collect?</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" t="inlineStr">
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>FAQ_Policies.json</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>156</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Question:
-                    What customer information does nenthom.com.vn collect?
-                    Answer:
-                    The website may collect first name, last name, email address, phon</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>What customer information does nenthom.com.vn collect?</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>2</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>FAQ_Policies.json</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>157</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Question:
-                    Does nenthom.com.vn sell customer information to third parties?
-                    Answer:
-                    No. Nenthom.com.vn commits not to trade or exchange custo</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>What customer information does nenthom.com.vn collect?</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>3</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>FAQ_Policies.json</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>174</v>
-      </c>
-      <c r="E24" t="inlineStr">
+      <c r="D11" t="n">
+        <v>314</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>Question:
                     What absolute commitment does nenthom.com.vn make regarding the commercial use of customer information?
@@ -1496,48 +1208,48 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>What customer information does nenthom.com.vn collect?</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>4</v>
-      </c>
-      <c r="C25" t="inlineStr">
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Chinh_sach_mua_hang.docx</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>11</v>
-      </c>
-      <c r="E25" t="inlineStr">
+      <c r="D12" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t># Privacy Policy
 To ensure website security and information security for consumers, nenthom.com.vn has issued a number of information security policies for individual and organizational customers whe</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>What customer information does nenthom.com.vn collect?</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>5</v>
-      </c>
-      <c r="C26" t="inlineStr">
+      <c r="B13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>FAQ_Candle_product.json</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>441</v>
-      </c>
-      <c r="E26" t="inlineStr">
+      <c r="D13" t="n">
+        <v>581</v>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>Question:
                     According to the official data privacy policy of nenthom.com.vn, how long is customer personal information stored?
@@ -1546,100 +1258,74 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>If a customer in Da Nang has not received any call from the postman after 3 days from placing an order, what specific action should they take according to the shipping policy?</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" t="inlineStr">
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>FAQ_Policies.json</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>146</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question:
-                    What should I do if I have not received my order after 3 days?
-                    Answer:
-                    You should contact nenthom.com.vn for support if you have </t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="D14" t="n">
+        <v>307</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Question:
+                    What action does nenthom.com.vn take immediately after receiving a customer's returned goods?
+                    Answer:
+                    Immediately after receiving</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>If a customer in Da Nang has not received any call from the postman after 3 days from placing an order, what specific action should they take according to the shipping policy?</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="B15" t="n">
         <v>2</v>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>FAQ_Policies.json</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>162</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question:
-                    Under what circumstances will nenthom.com.vn's customer service call a customer regarding a delivery delay within Hanoi or Ho Chi Minh City?
-                    Answer:
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>If a customer in Da Nang has not received any call from the postman after 3 days from placing an order, what specific action should they take according to the shipping policy?</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>3</v>
-      </c>
-      <c r="C29" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Chinh_sach_mua_hang.docx</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>8</v>
-      </c>
-      <c r="E29" t="inlineStr">
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>## Average delivery time:
 Orders within Hanoi or Ho Chi Minh: Customers will receive within a maximum of 24 hours (Usually 2-4 hours) from the time of order. Except for pre-orders or insufficient inv</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>If a customer in Da Nang has not received any call from the postman after 3 days from placing an order, what specific action should they take according to the shipping policy?</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>4</v>
-      </c>
-      <c r="C30" t="inlineStr">
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>FAQ_Candle_product.json</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>509</v>
-      </c>
-      <c r="E30" t="inlineStr">
+      <c r="D16" t="n">
+        <v>649</v>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>Question:
                     How does nenthom.com.vn handle local Hanoi delivery orders if a sudden inventory deficit occurs?
@@ -1648,76 +1334,24 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>If a customer in Da Nang has not received any call from the postman after 3 days from placing an order, what specific action should they take according to the shipping policy?</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>5</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>FAQ_Policies.json</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>167</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Question:
-                    What action does nenthom.com.vn take immediately after receiving a customer's returned goods?
-                    Answer:
-                    Immediately after receiving</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Detail the full workflow for a customer who wants to exchange a product, starting from the notification step to the point they receive a replacement.</t>
         </is>
       </c>
-      <c r="B32" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" t="inlineStr">
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>FAQ_Candle_product.json</t>
         </is>
       </c>
-      <c r="D32" t="n">
-        <v>451</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question:
-                    Under the merchandise return framework, at what exact point will nenthom.com.vn dispatch a replacement order to the customer?
-                    Answer:
-               </t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Detail the full workflow for a customer who wants to exchange a product, starting from the notification step to the point they receive a replacement.</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>2</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>FAQ_Candle_product.json</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>455</v>
-      </c>
-      <c r="E33" t="inlineStr">
+      <c r="D17" t="n">
+        <v>595</v>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t xml:space="preserve">Question:
                     What are the mandatory product condition parameters for a customer to claim a full return or exchange within the 7-day window?
@@ -1726,24 +1360,50 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Detail the full workflow for a customer who wants to exchange a product, starting from the notification step to the point they receive a replacement.</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>FAQ_Policies.json</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>295</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Question:
+                    What is the first step in the return process?
+                    Answer:
+                    The first step is to notify nenthom.com.vn through the Fanpage or hotline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Detail the full workflow for a customer who wants to exchange a product, starting from the notification step to the point they receive a replacement.</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
         <v>3</v>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Chinh_sach_mua_hang.docx</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
+      <c r="D19" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>## Conditions for returning the product:
 The product is still intact with all parts, showing no signs of heavy use or damage.
@@ -1751,154 +1411,24 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Detail the full workflow for a customer who wants to exchange a product, starting from the notification step to the point they receive a replacement.</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>4</v>
-      </c>
-      <c r="C35" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>According to the Privacy Policy, under what two specific governmental or legal conditions can nenthom.com.vn reasonably share customer information without violating its policies?</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>FAQ_Policies.json</t>
         </is>
       </c>
-      <c r="D35" t="n">
-        <v>167</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Question:
-                    What action does nenthom.com.vn take immediately after receiving a customer's returned goods?
-                    Answer:
-                    Immediately after receiving</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Detail the full workflow for a customer who wants to exchange a product, starting from the notification step to the point they receive a replacement.</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>5</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>FAQ_Policies.json</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>155</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Question:
-                    What is the first step in the return process?
-                    Answer:
-                    The first step is to notify nenthom.com.vn through the Fanpage or hotline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>According to the Privacy Policy, under what two specific governmental or legal conditions can nenthom.com.vn reasonably share customer information without violating its policies?</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>FAQ_Policies.json</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>158</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Question:
-                    Can customer information be shared in special cases?
-                    Answer:
-                    Yes. Information may be shared with customer consent, to comply with</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>According to the Privacy Policy, under what two specific governmental or legal conditions can nenthom.com.vn reasonably share customer information without violating its policies?</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>2</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>FAQ_Policies.json</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>174</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Question:
-                    What absolute commitment does nenthom.com.vn make regarding the commercial use of customer information?
-                    Answer:
-                    The website commi</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>According to the Privacy Policy, under what two specific governmental or legal conditions can nenthom.com.vn reasonably share customer information without violating its policies?</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>3</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>FAQ_Policies.json</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>157</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Question:
-                    Does nenthom.com.vn sell customer information to third parties?
-                    Answer:
-                    No. Nenthom.com.vn commits not to trade or exchange custo</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>According to the Privacy Policy, under what two specific governmental or legal conditions can nenthom.com.vn reasonably share customer information without violating its policies?</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>4</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>FAQ_Policies.json</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>171</v>
-      </c>
-      <c r="E40" t="inlineStr">
+      <c r="D20" t="n">
+        <v>311</v>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t xml:space="preserve">Question:
                     Under what condition can customer information be legally disclosed to protect the interests of the company and its partners?
@@ -1907,24 +1437,24 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>According to the Privacy Policy, under what two specific governmental or legal conditions can nenthom.com.vn reasonably share customer information without violating its policies?</t>
         </is>
       </c>
-      <c r="B41" t="n">
-        <v>5</v>
-      </c>
-      <c r="C41" t="inlineStr">
+      <c r="B21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>FAQ_Candle_product.json</t>
         </is>
       </c>
-      <c r="D41" t="n">
-        <v>464</v>
-      </c>
-      <c r="E41" t="inlineStr">
+      <c r="D21" t="n">
+        <v>604</v>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>Question:
                     In what specific context does nenthom.com.vn explicitly state it will notify customers prior to sharing their personal data with external entities?
@@ -1932,50 +1462,50 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>What are the geographical scopes collected by nenthom.com.vn below the country level to process an order?</t>
         </is>
       </c>
-      <c r="B42" t="n">
-        <v>1</v>
-      </c>
-      <c r="C42" t="inlineStr">
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>FAQ_Policies.json</t>
         </is>
       </c>
-      <c r="D42" t="n">
-        <v>156</v>
-      </c>
-      <c r="E42" t="inlineStr">
+      <c r="D22" t="n">
+        <v>297</v>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>Question:
-                    What customer information does nenthom.com.vn collect?
-                    Answer:
-                    The website may collect first name, last name, email address, phon</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+                    Does nenthom.com.vn sell customer information to third parties?
+                    Answer:
+                    No. Nenthom.com.vn commits not to trade or exchange custo</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>What are the geographical scopes collected by nenthom.com.vn below the country level to process an order?</t>
         </is>
       </c>
-      <c r="B43" t="n">
+      <c r="B23" t="n">
         <v>2</v>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>FAQ_Candle_product.json</t>
         </is>
       </c>
-      <c r="D43" t="n">
-        <v>454</v>
-      </c>
-      <c r="E43" t="inlineStr">
+      <c r="D23" t="n">
+        <v>594</v>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>Question:
                     What specific personal identifying items fall within the standard data collection scope of the nenthom.com.vn platform?
@@ -1984,204 +1514,74 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>What are the geographical scopes collected by nenthom.com.vn below the country level to process an order?</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>3</v>
-      </c>
-      <c r="C44" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Explain how the delivery time expectations and handling process differ for an order inside Hanoi versus an order intended as a holiday gift for an outside area.</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>FAQ_Policies.json</t>
         </is>
       </c>
-      <c r="D44" t="n">
-        <v>140</v>
-      </c>
-      <c r="E44" t="inlineStr">
+      <c r="D24" t="n">
+        <v>285</v>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>Question:
-                    Does nenthom.com.vn ship nationwide in Vietnam?
-                    Answer:
-                    Yes. Nenthom.com.vn ships to almost every region in Vietnam.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>What are the geographical scopes collected by nenthom.com.vn below the country level to process an order?</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
+                    How long does delivery take to other areas in Vietnam?
+                    Answer:
+                    Delivery usually takes 1–2 days and may take up to 3 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Explain how the delivery time expectations and handling process differ for an order inside Hanoi versus an order intended as a holiday gift for an outside area.</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Chinh_sach_mua_hang.docx</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>4</v>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>FAQ_Policies.json</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>141</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Question:
-                    Which delivery partners does nenthom.com.vn work with?
-                    Answer:
-                    Nenthom.com.vn works with Giao Hang Tiet Kiem, Giao Hang Nhanh, Vi</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>What are the geographical scopes collected by nenthom.com.vn below the country level to process an order?</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>5</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>FAQ_Policies.json</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>157</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Question:
-                    Does nenthom.com.vn sell customer information to third parties?
-                    Answer:
-                    No. Nenthom.com.vn commits not to trade or exchange custo</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Explain how the delivery time expectations and handling process differ for an order inside Hanoi versus an order intended as a holiday gift for an outside area.</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>FAQ_Policies.json</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>177</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Question:
-                    What is the expected delivery timeframe if a customer is located outside Hanoi and Ho Chi Minh City?
-                    Answer:
-                    The average delivery</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Explain how the delivery time expectations and handling process differ for an order inside Hanoi versus an order intended as a holiday gift for an outside area.</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>2</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Chinh_sach_mua_hang.docx</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>8</v>
-      </c>
-      <c r="E48" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>## Average delivery time:
 Orders within Hanoi or Ho Chi Minh: Customers will receive within a maximum of 24 hours (Usually 2-4 hours) from the time of order. Except for pre-orders or insufficient inv</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Explain how the delivery time expectations and handling process differ for an order inside Hanoi versus an order intended as a holiday gift for an outside area.</t>
         </is>
       </c>
-      <c r="B49" t="n">
+      <c r="B26" t="n">
         <v>3</v>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>FAQ_Policies.json</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>144</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Question:
-                    How long does delivery take within Hanoi or Ho Chi Minh City?
-                    Answer:
-                    Orders are usually delivered within 2–4 hours and no later </t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Explain how the delivery time expectations and handling process differ for an order inside Hanoi versus an order intended as a holiday gift for an outside area.</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>4</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>FAQ_Policies.json</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>145</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Question:
-                    How long does delivery take to other areas in Vietnam?
-                    Answer:
-                    Delivery usually takes 1–2 days and may take up to 3 days.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Explain how the delivery time expectations and handling process differ for an order inside Hanoi versus an order intended as a holiday gift for an outside area.</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>5</v>
-      </c>
-      <c r="C51" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>FAQ_Candle_product.json</t>
         </is>
       </c>
-      <c r="D51" t="n">
-        <v>509</v>
-      </c>
-      <c r="E51" t="inlineStr">
+      <c r="D26" t="n">
+        <v>649</v>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t>Question:
                     How does nenthom.com.vn handle local Hanoi delivery orders if a sudden inventory deficit occurs?
